--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/XRF/Panel 02/front/xrf_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/XRF/Panel 02/front/xrf_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.06825</v>
+        <v>17.26674</v>
       </c>
       <c r="D2" t="n">
-        <v>16.88755</v>
+        <v>17.17754</v>
       </c>
       <c r="E2" t="n">
-        <v>17.08398</v>
+        <v>17.23391</v>
       </c>
       <c r="F2" t="n">
-        <v>44.51452</v>
+        <v>43.80191</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05204</v>
+        <v>0.05116</v>
       </c>
       <c r="H2" t="n">
-        <v>1.83414</v>
+        <v>1.85992</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.20782</v>
+        <v>17.10222</v>
       </c>
       <c r="D3" t="n">
-        <v>17.09943</v>
+        <v>17.00351</v>
       </c>
       <c r="E3" t="n">
-        <v>16.99781</v>
+        <v>17.06871</v>
       </c>
       <c r="F3" t="n">
-        <v>43.74952</v>
+        <v>43.28851</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05264</v>
+        <v>0.05093</v>
       </c>
       <c r="H3" t="n">
-        <v>1.87985</v>
+        <v>1.90063</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.13088</v>
+        <v>17.30605</v>
       </c>
       <c r="D4" t="n">
-        <v>17.16193</v>
+        <v>16.86172</v>
       </c>
       <c r="E4" t="n">
-        <v>17.23202</v>
+        <v>17.22896</v>
       </c>
       <c r="F4" t="n">
-        <v>43.67613</v>
+        <v>43.40734</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0508</v>
+        <v>0.0516</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8684</v>
+        <v>1.88396</v>
       </c>
     </row>
   </sheetData>
